--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,766 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9621,0.0023,0.0254,0.0024</t>
-  </si>
-  <si>
-    <t>0.9140,0.0009,0.0056,0.0606</t>
-  </si>
-  <si>
-    <t>0.9333,0.0116,0.0184,0.0126</t>
-  </si>
-  <si>
-    <t>0.9498,0.0010,0.0042,0.0261</t>
-  </si>
-  <si>
-    <t>0.9794,0.0024,0.0010,0.0087</t>
-  </si>
-  <si>
-    <t>0.9316,0.0161,0.0038,0.0113</t>
-  </si>
-  <si>
-    <t>0.9320,0.0185,0.0122,0.0143</t>
-  </si>
-  <si>
-    <t>0.9436,0.0123,0.0047,0.0121</t>
-  </si>
-  <si>
-    <t>0.9755,0.0013,0.0016,0.0160</t>
-  </si>
-  <si>
-    <t>0.9494,0.0044,0.0016,0.0318</t>
-  </si>
-  <si>
-    <t>0.9519,0.0045,0.0036,0.0250</t>
-  </si>
-  <si>
-    <t>0.9617,0.0040,0.0047,0.0190</t>
-  </si>
-  <si>
-    <t>0.9457,0.0043,0.0686,0.0011</t>
-  </si>
-  <si>
-    <t>0.8614,0.0077,0.2088,0.0024</t>
-  </si>
-  <si>
-    <t>0.8340,0.0055,0.3126,0.0011</t>
-  </si>
-  <si>
-    <t>0.8271,0.0053,0.2583,0.0025</t>
-  </si>
-  <si>
-    <t>0.9499,0.0040,0.0544,0.0016</t>
-  </si>
-  <si>
-    <t>0.8037,0.0708,0.0925,0.0009</t>
-  </si>
-  <si>
-    <t>0.5408,0.3020,0.1430,0.0022</t>
-  </si>
-  <si>
-    <t>0.9461,0.0107,0.0279,0.0029</t>
-  </si>
-  <si>
-    <t>0.4781,0.3787,0.1906,0.0076</t>
-  </si>
-  <si>
-    <t>0.5734,0.4428,0.0313,0.0004</t>
-  </si>
-  <si>
-    <t>0.7477,0.0041,0.4805,0.0013</t>
-  </si>
-  <si>
-    <t>0.9288,0.0042,0.0932,0.0010</t>
-  </si>
-  <si>
-    <t>0.1600,0.0057,0.9465,0.0004</t>
-  </si>
-  <si>
-    <t>0.9188,0.0014,0.1508,0.0009</t>
-  </si>
-  <si>
-    <t>0.6187,0.0038,0.6732,0.0007</t>
-  </si>
-  <si>
-    <t>0.5347,0.0048,0.7339,0.0013</t>
-  </si>
-  <si>
-    <t>0.0490,0.0070,0.9756,0.0010</t>
-  </si>
-  <si>
-    <t>0.9610,0.0061,0.0294,0.0014</t>
-  </si>
-  <si>
-    <t>0.8235,0.0968,0.0668,0.0054</t>
-  </si>
-  <si>
-    <t>0.0332,0.0827,0.9662,0.0058</t>
-  </si>
-  <si>
-    <t>0.7086,0.0793,0.2397,0.0051</t>
-  </si>
-  <si>
-    <t>0.9513,0.0044,0.0378,0.0033</t>
-  </si>
-  <si>
-    <t>0.7988,0.0325,0.1743,0.0223</t>
-  </si>
-  <si>
-    <t>0.7438,0.1368,0.1261,0.0107</t>
-  </si>
-  <si>
-    <t>0.9044,0.0415,0.0343,0.0045</t>
-  </si>
-  <si>
-    <t>0.1312,0.6868,0.3190,0.0015</t>
-  </si>
-  <si>
-    <t>0.6983,0.0086,0.3958,0.0040</t>
-  </si>
-  <si>
-    <t>0.3880,0.0208,0.7724,0.0008</t>
-  </si>
-  <si>
-    <t>0.0255,0.0042,0.9831,0.0004</t>
-  </si>
-  <si>
-    <t>0.6139,0.0406,0.4694,0.0008</t>
-  </si>
-  <si>
-    <t>0.2131,0.7313,0.1267,0.0010</t>
-  </si>
-  <si>
-    <t>0.7255,0.0100,0.4519,0.0009</t>
-  </si>
-  <si>
-    <t>0.8142,0.0189,0.1539,0.0206</t>
-  </si>
-  <si>
-    <t>0.9451,0.0108,0.0274,0.0011</t>
-  </si>
-  <si>
-    <t>0.5936,0.2270,0.1343,0.0018</t>
-  </si>
-  <si>
-    <t>0.8967,0.0403,0.0382,0.0020</t>
-  </si>
-  <si>
-    <t>0.0197,0.0098,0.9831,0.0004</t>
-  </si>
-  <si>
-    <t>0.0097,0.4365,0.9771,0.0004</t>
-  </si>
-  <si>
-    <t>0.9497,0.0021,0.0727,0.0014</t>
-  </si>
-  <si>
-    <t>0.0422,0.0234,0.9801,0.0006</t>
-  </si>
-  <si>
-    <t>0.0087,0.0062,0.9941,0.0003</t>
-  </si>
-  <si>
-    <t>0.1993,0.0685,0.8604,0.0011</t>
-  </si>
-  <si>
-    <t>0.9606,0.0095,0.0051,0.0071</t>
-  </si>
-  <si>
-    <t>0.9741,0.0017,0.0020,0.0115</t>
-  </si>
-  <si>
-    <t>0.7993,0.0649,0.1269,0.0356</t>
-  </si>
-  <si>
-    <t>0.0587,0.3463,0.9034,0.0043</t>
-  </si>
-  <si>
-    <t>0.9738,0.0064,0.0053,0.0043</t>
-  </si>
-  <si>
-    <t>0.9502,0.0081,0.0063,0.0124</t>
-  </si>
-  <si>
-    <t>0.9355,0.0174,0.0070,0.0113</t>
-  </si>
-  <si>
-    <t>0.1452,0.1818,0.8337,0.0016</t>
-  </si>
-  <si>
-    <t>0.1587,0.0492,0.9256,0.0005</t>
-  </si>
-  <si>
-    <t>0.2514,0.0486,0.8135,0.0007</t>
-  </si>
-  <si>
-    <t>0.0703,0.6832,0.5850,0.0009</t>
-  </si>
-  <si>
-    <t>0.0636,0.0089,0.9681,0.0005</t>
-  </si>
-  <si>
-    <t>0.7422,0.1649,0.0602,0.0016</t>
-  </si>
-  <si>
-    <t>0.0307,0.9605,0.1668,0.0006</t>
-  </si>
-  <si>
-    <t>0.7436,0.0461,0.3631,0.0079</t>
-  </si>
-  <si>
-    <t>0.8842,0.0135,0.1182,0.0035</t>
-  </si>
-  <si>
-    <t>0.0109,0.2412,0.9815,0.0010</t>
-  </si>
-  <si>
-    <t>0.1293,0.2348,0.7820,0.0006</t>
-  </si>
-  <si>
-    <t>0.6419,0.0371,0.4369,0.0009</t>
-  </si>
-  <si>
-    <t>0.0261,0.8111,0.7409,0.0011</t>
-  </si>
-  <si>
-    <t>0.0202,0.6427,0.9287,0.0008</t>
-  </si>
-  <si>
-    <t>0.7132,0.0012,0.0276,0.2155</t>
-  </si>
-  <si>
-    <t>0.5251,0.0009,0.0161,0.5210</t>
-  </si>
-  <si>
-    <t>0.8007,0.0007,0.0129,0.1550</t>
-  </si>
-  <si>
-    <t>0.7930,0.0068,0.0189,0.1952</t>
-  </si>
-  <si>
-    <t>0.8231,0.0079,0.0768,0.0497</t>
-  </si>
-  <si>
-    <t>0.8728,0.0011,0.0138,0.0763</t>
-  </si>
-  <si>
-    <t>0.0850,0.2590,0.9116,0.0013</t>
-  </si>
-  <si>
-    <t>0.0196,0.2187,0.9736,0.0002</t>
-  </si>
-  <si>
-    <t>0.1578,0.1251,0.8584,0.0010</t>
-  </si>
-  <si>
-    <t>0.0473,0.0720,0.9436,0.0005</t>
-  </si>
-  <si>
-    <t>0.0239,0.7196,0.9073,0.0013</t>
-  </si>
-  <si>
-    <t>0.2568,0.0933,0.7787,0.0004</t>
-  </si>
-  <si>
-    <t>0.9496,0.0134,0.0141,0.0056</t>
-  </si>
-  <si>
-    <t>0.9701,0.0068,0.0044,0.0054</t>
-  </si>
-  <si>
-    <t>0.9458,0.0182,0.0053,0.0074</t>
-  </si>
-  <si>
-    <t>0.9391,0.0129,0.0086,0.0165</t>
-  </si>
-  <si>
-    <t>0.9843,0.0013,0.0008,0.0060</t>
-  </si>
-  <si>
-    <t>0.8864,0.0050,0.0026,0.1065</t>
-  </si>
-  <si>
-    <t>0.9818,0.0036,0.0022,0.0027</t>
-  </si>
-  <si>
-    <t>0.9523,0.0107,0.0051,0.0131</t>
-  </si>
-  <si>
-    <t>0.9106,0.0066,0.0109,0.0674</t>
-  </si>
-  <si>
-    <t>0.9160,0.0139,0.0060,0.0281</t>
-  </si>
-  <si>
-    <t>0.9642,0.0039,0.0017,0.0255</t>
-  </si>
-  <si>
-    <t>0.9351,0.0081,0.0085,0.0353</t>
-  </si>
-  <si>
-    <t>0.9581,0.0046,0.0011,0.0181</t>
-  </si>
-  <si>
-    <t>0.9109,0.0138,0.0124,0.0322</t>
-  </si>
-  <si>
-    <t>0.9609,0.0062,0.0018,0.0107</t>
-  </si>
-  <si>
-    <t>0.9597,0.0032,0.0054,0.0209</t>
-  </si>
-  <si>
-    <t>0.4077,0.0147,0.8174,0.0007</t>
-  </si>
-  <si>
-    <t>0.4514,0.0276,0.7119,0.0017</t>
-  </si>
-  <si>
-    <t>0.9677,0.0010,0.0378,0.0009</t>
-  </si>
-  <si>
-    <t>0.4548,0.0146,0.7253,0.0011</t>
-  </si>
-  <si>
-    <t>0.6685,0.1861,0.1420,0.0053</t>
-  </si>
-  <si>
-    <t>0.5483,0.1706,0.4181,0.0049</t>
-  </si>
-  <si>
-    <t>0.6763,0.2112,0.1247,0.0098</t>
-  </si>
-  <si>
-    <t>0.9234,0.0135,0.0458,0.0065</t>
-  </si>
-  <si>
-    <t>0.6078,0.2379,0.1405,0.0055</t>
-  </si>
-  <si>
-    <t>0.2188,0.7608,0.0730,0.0010</t>
-  </si>
-  <si>
-    <t>0.9246,0.0290,0.0279,0.0045</t>
-  </si>
-  <si>
-    <t>0.8354,0.0071,0.1988,0.0060</t>
-  </si>
-  <si>
-    <t>0.4745,0.0153,0.6842,0.0038</t>
-  </si>
-  <si>
-    <t>0.9800,0.0011,0.0143,0.0007</t>
-  </si>
-  <si>
-    <t>0.8250,0.0085,0.2637,0.0049</t>
-  </si>
-  <si>
-    <t>0.6691,0.0342,0.4327,0.0159</t>
-  </si>
-  <si>
-    <t>0.9056,0.0633,0.0139,0.0009</t>
-  </si>
-  <si>
-    <t>0.8918,0.0554,0.0226,0.0008</t>
-  </si>
-  <si>
-    <t>0.6695,0.0602,0.3618,0.0141</t>
-  </si>
-  <si>
-    <t>0.1173,0.8204,0.1694,0.0004</t>
-  </si>
-  <si>
-    <t>0.8615,0.0553,0.0740,0.0027</t>
-  </si>
-  <si>
-    <t>0.8999,0.0202,0.0545,0.0082</t>
-  </si>
-  <si>
-    <t>0.8248,0.0759,0.0749,0.0133</t>
-  </si>
-  <si>
-    <t>0.9181,0.0345,0.0419,0.0043</t>
-  </si>
-  <si>
-    <t>0.9437,0.0048,0.0118,0.0210</t>
-  </si>
-  <si>
-    <t>0.8903,0.0358,0.0314,0.0223</t>
-  </si>
-  <si>
-    <t>0.9290,0.0032,0.0106,0.0298</t>
-  </si>
-  <si>
-    <t>0.9838,0.0020,0.0025,0.0047</t>
-  </si>
-  <si>
-    <t>0.9680,0.0068,0.0124,0.0032</t>
-  </si>
-  <si>
-    <t>0.9060,0.0152,0.0097,0.0293</t>
-  </si>
-  <si>
-    <t>0.9543,0.0089,0.0081,0.0127</t>
-  </si>
-  <si>
-    <t>0.0687,0.0157,0.9676,0.0003</t>
-  </si>
-  <si>
-    <t>0.1354,0.1137,0.9009,0.0004</t>
-  </si>
-  <si>
-    <t>0.4602,0.0190,0.7158,0.0005</t>
-  </si>
-  <si>
-    <t>0.2523,0.0601,0.8148,0.0007</t>
-  </si>
-  <si>
-    <t>0.9354,0.0017,0.0666,0.0028</t>
-  </si>
-  <si>
-    <t>0.9114,0.0037,0.1223,0.0027</t>
-  </si>
-  <si>
-    <t>0.5515,0.0098,0.6052,0.0070</t>
-  </si>
-  <si>
-    <t>0.9079,0.0117,0.0921,0.0027</t>
-  </si>
-  <si>
-    <t>0.8730,0.0064,0.0265,0.0650</t>
-  </si>
-  <si>
-    <t>0.0753,0.0011,0.0056,0.9676</t>
-  </si>
-  <si>
-    <t>0.4536,0.0031,0.0705,0.3816</t>
-  </si>
-  <si>
-    <t>0.9578,0.0013,0.0188,0.0059</t>
-  </si>
-  <si>
-    <t>0.1047,0.1968,0.8768,0.0008</t>
-  </si>
-  <si>
-    <t>0.9190,0.0094,0.0360,0.0237</t>
-  </si>
-  <si>
-    <t>0.9586,0.0067,0.0104,0.0060</t>
-  </si>
-  <si>
-    <t>0.9692,0.0046,0.0071,0.0069</t>
-  </si>
-  <si>
-    <t>0.9515,0.0111,0.0114,0.0077</t>
-  </si>
-  <si>
-    <t>0.8835,0.0186,0.0449,0.0371</t>
-  </si>
-  <si>
-    <t>0.9547,0.0063,0.0071,0.0186</t>
-  </si>
-  <si>
-    <t>0.8759,0.0381,0.0233,0.0167</t>
-  </si>
-  <si>
-    <t>0.7690,0.0109,0.2924,0.0193</t>
-  </si>
-  <si>
-    <t>0.7420,0.0024,0.0466,0.1241</t>
-  </si>
-  <si>
-    <t>0.9448,0.0037,0.0154,0.0241</t>
-  </si>
-  <si>
-    <t>0.9274,0.0126,0.0323,0.0035</t>
-  </si>
-  <si>
-    <t>0.9434,0.0125,0.0227,0.0049</t>
-  </si>
-  <si>
-    <t>0.9269,0.0108,0.0346,0.0091</t>
-  </si>
-  <si>
-    <t>0.7726,0.0315,0.2392,0.0160</t>
-  </si>
-  <si>
-    <t>0.8580,0.0255,0.1126,0.0021</t>
-  </si>
-  <si>
-    <t>0.9748,0.0030,0.0129,0.0014</t>
-  </si>
-  <si>
-    <t>0.8424,0.0803,0.0409,0.0117</t>
-  </si>
-  <si>
-    <t>0.9657,0.0044,0.0035,0.0157</t>
-  </si>
-  <si>
-    <t>0.9395,0.0094,0.0098,0.0156</t>
-  </si>
-  <si>
-    <t>0.9132,0.0138,0.0200,0.0274</t>
-  </si>
-  <si>
-    <t>0.9530,0.0125,0.0103,0.0040</t>
-  </si>
-  <si>
-    <t>0.9633,0.0078,0.0128,0.0069</t>
-  </si>
-  <si>
-    <t>0.8804,0.0394,0.0308,0.0236</t>
-  </si>
-  <si>
-    <t>0.9562,0.0090,0.0039,0.0115</t>
-  </si>
-  <si>
-    <t>0.8791,0.0234,0.0627,0.0109</t>
-  </si>
-  <si>
-    <t>0.8895,0.0459,0.0383,0.0062</t>
-  </si>
-  <si>
-    <t>0.6827,0.0889,0.2913,0.0193</t>
-  </si>
-  <si>
-    <t>0.9301,0.0311,0.0192,0.0046</t>
-  </si>
-  <si>
-    <t>0.9216,0.0281,0.0290,0.0034</t>
-  </si>
-  <si>
-    <t>0.8956,0.0450,0.0267,0.0050</t>
-  </si>
-  <si>
-    <t>0.9828,0.0029,0.0020,0.0029</t>
-  </si>
-  <si>
-    <t>0.9721,0.0057,0.0059,0.0032</t>
-  </si>
-  <si>
-    <t>0.0179,0.0891,0.9787,0.0011</t>
-  </si>
-  <si>
-    <t>0.9395,0.0171,0.0062,0.0081</t>
-  </si>
-  <si>
-    <t>0.0273,0.0287,0.9807,0.0004</t>
-  </si>
-  <si>
-    <t>0.5706,0.0079,0.7269,0.0012</t>
-  </si>
-  <si>
-    <t>0.9000,0.0018,0.1893,0.0016</t>
-  </si>
-  <si>
-    <t>0.3416,0.0554,0.7396,0.0030</t>
-  </si>
-  <si>
-    <t>0.6572,0.0083,0.6038,0.0010</t>
-  </si>
-  <si>
-    <t>0.0037,0.0348,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.4655,0.0112,0.6488,0.0039</t>
-  </si>
-  <si>
-    <t>0.7330,0.0179,0.4166,0.0027</t>
-  </si>
-  <si>
-    <t>0.9387,0.0033,0.0925,0.0011</t>
-  </si>
-  <si>
-    <t>0.9701,0.0019,0.0225,0.0010</t>
-  </si>
-  <si>
-    <t>0.9351,0.0056,0.0787,0.0009</t>
-  </si>
-  <si>
-    <t>0.6756,0.0570,0.3593,0.0054</t>
-  </si>
-  <si>
-    <t>0.8198,0.0109,0.3448,0.0015</t>
-  </si>
-  <si>
-    <t>0.8773,0.0093,0.1292,0.0068</t>
-  </si>
-  <si>
-    <t>0.8799,0.0122,0.1123,0.0077</t>
-  </si>
-  <si>
-    <t>0.8303,0.0806,0.0546,0.0106</t>
-  </si>
-  <si>
-    <t>0.9447,0.0209,0.0049,0.0044</t>
-  </si>
-  <si>
-    <t>0.6370,0.3360,0.0219,0.0033</t>
-  </si>
-  <si>
-    <t>0.9599,0.0104,0.0050,0.0059</t>
-  </si>
-  <si>
-    <t>0.9199,0.0380,0.0217,0.0048</t>
-  </si>
-  <si>
-    <t>0.9429,0.0065,0.0457,0.0016</t>
-  </si>
-  <si>
-    <t>0.8812,0.0013,0.1558,0.0019</t>
-  </si>
-  <si>
-    <t>0.9443,0.0021,0.0670,0.0020</t>
-  </si>
-  <si>
-    <t>0.9568,0.0038,0.0397,0.0005</t>
-  </si>
-  <si>
-    <t>0.8896,0.0024,0.1620,0.0024</t>
-  </si>
-  <si>
-    <t>0.3476,0.0105,0.7549,0.0055</t>
-  </si>
-  <si>
-    <t>0.2963,0.0584,0.7967,0.0071</t>
-  </si>
-  <si>
-    <t>0.1783,0.0738,0.8880,0.0041</t>
-  </si>
-  <si>
-    <t>0.4526,0.0128,0.7478,0.0009</t>
-  </si>
-  <si>
-    <t>0.4432,0.0086,0.7813,0.0006</t>
-  </si>
-  <si>
-    <t>0.9112,0.0189,0.0183,0.0310</t>
-  </si>
-  <si>
-    <t>0.9747,0.0052,0.0048,0.0038</t>
-  </si>
-  <si>
-    <t>0.9312,0.0201,0.0261,0.0079</t>
-  </si>
-  <si>
-    <t>0.9618,0.0048,0.0041,0.0117</t>
-  </si>
-  <si>
-    <t>0.9064,0.0413,0.0126,0.0106</t>
-  </si>
-  <si>
-    <t>0.9382,0.0150,0.0123,0.0134</t>
-  </si>
-  <si>
-    <t>0.9673,0.0056,0.0015,0.0091</t>
-  </si>
-  <si>
-    <t>0.9565,0.0139,0.0100,0.0053</t>
-  </si>
-  <si>
-    <t>0.6724,0.0489,0.4698,0.0075</t>
-  </si>
-  <si>
-    <t>0.9081,0.0130,0.1127,0.0035</t>
-  </si>
-  <si>
-    <t>0.8966,0.0224,0.0567,0.0160</t>
-  </si>
-  <si>
-    <t>0.0208,0.0524,0.9868,0.0004</t>
-  </si>
-  <si>
-    <t>0.0286,0.0302,0.9688,0.0015</t>
-  </si>
-  <si>
-    <t>0.7205,0.0069,0.5068,0.0006</t>
-  </si>
-  <si>
-    <t>0.0032,0.0050,0.9952,0.0002</t>
-  </si>
-  <si>
-    <t>0.8075,0.0043,0.4157,0.0003</t>
-  </si>
-  <si>
-    <t>0.0332,0.0135,0.9836,0.0005</t>
-  </si>
-  <si>
-    <t>0.1094,0.0094,0.9418,0.0005</t>
-  </si>
-  <si>
-    <t>0.2200,0.0234,0.8907,0.0013</t>
-  </si>
-  <si>
-    <t>0.9645,0.0009,0.0254,0.0025</t>
-  </si>
-  <si>
-    <t>0.8690,0.0064,0.1711,0.0039</t>
-  </si>
-  <si>
-    <t>0.8848,0.0016,0.2183,0.0008</t>
-  </si>
-  <si>
-    <t>0.9519,0.0044,0.0047,0.0203</t>
-  </si>
-  <si>
-    <t>0.9619,0.0056,0.0022,0.0153</t>
-  </si>
-  <si>
-    <t>0.9765,0.0048,0.0027,0.0065</t>
-  </si>
-  <si>
-    <t>0.9060,0.0275,0.0100,0.0155</t>
-  </si>
-  <si>
-    <t>0.9557,0.0074,0.0026,0.0124</t>
-  </si>
-  <si>
-    <t>0.9769,0.0019,0.0019,0.0075</t>
-  </si>
-  <si>
-    <t>0.9486,0.0098,0.0018,0.0113</t>
-  </si>
-  <si>
-    <t>0.9690,0.0012,0.0007,0.0228</t>
-  </si>
-  <si>
-    <t>0.4714,0.0332,0.6683,0.0010</t>
-  </si>
-  <si>
-    <t>0.2496,0.0218,0.8883,0.0007</t>
-  </si>
-  <si>
-    <t>0.1565,0.0182,0.9343,0.0002</t>
-  </si>
-  <si>
-    <t>0.6854,0.0299,0.4490,0.0021</t>
-  </si>
-  <si>
-    <t>0.1413,0.0231,0.9384,0.0017</t>
-  </si>
-  <si>
-    <t>0.9056,0.0010,0.1296,0.0016</t>
-  </si>
-  <si>
-    <t>0.8636,0.0018,0.2387,0.0010</t>
-  </si>
-  <si>
-    <t>0.5874,0.0200,0.5376,0.0047</t>
-  </si>
-  <si>
-    <t>0.9269,0.0104,0.0293,0.0077</t>
-  </si>
-  <si>
-    <t>0.8362,0.0030,0.0587,0.0347</t>
-  </si>
-  <si>
-    <t>0.6991,0.0011,0.0177,0.2430</t>
-  </si>
-  <si>
-    <t>0.9252,0.0003,0.0058,0.0284</t>
-  </si>
-  <si>
-    <t>0.9491,0.0002,0.0051,0.0254</t>
-  </si>
-  <si>
-    <t>0.8697,0.0082,0.0739,0.0160</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9595,0.0212,0.0036,0.0087</t>
+  </si>
+  <si>
+    <t>0.0664,0.0011,0.0002,0.9791</t>
+  </si>
+  <si>
+    <t>0.5845,0.0381,0.0027,0.3314</t>
+  </si>
+  <si>
+    <t>0.1162,0.0036,0.0016,0.9537</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0015,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0006,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0014,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.6810,0.1175,0.1969,0.0063</t>
+  </si>
+  <si>
+    <t>0.0947,0.0625,0.8775,0.0043</t>
+  </si>
+  <si>
+    <t>0.1997,0.0068,0.9260,0.0010</t>
+  </si>
+  <si>
+    <t>0.0742,0.0023,0.9609,0.0005</t>
+  </si>
+  <si>
+    <t>0.8371,0.0300,0.1024,0.0137</t>
+  </si>
+  <si>
+    <t>0.0008,0.9979,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9981,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.3007,0.8604,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.0225,0.9740,0.0082,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.9984,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7277,0.0125,0.3363,0.0116</t>
+  </si>
+  <si>
+    <t>0.3790,0.0187,0.7114,0.0040</t>
+  </si>
+  <si>
+    <t>0.0112,0.0032,0.9891,0.0004</t>
+  </si>
+  <si>
+    <t>0.2689,0.0180,0.7454,0.0079</t>
+  </si>
+  <si>
+    <t>0.3990,0.0075,0.8037,0.0021</t>
+  </si>
+  <si>
+    <t>0.0184,0.0029,0.9791,0.0034</t>
+  </si>
+  <si>
+    <t>0.0089,0.0013,0.9924,0.0017</t>
+  </si>
+  <si>
+    <t>0.1422,0.9026,0.0048,0.0007</t>
+  </si>
+  <si>
+    <t>0.6321,0.1746,0.1655,0.0030</t>
+  </si>
+  <si>
+    <t>0.0052,0.0201,0.9901,0.0084</t>
+  </si>
+  <si>
+    <t>0.0580,0.8797,0.0327,0.0004</t>
+  </si>
+  <si>
+    <t>0.8588,0.1282,0.0238,0.0081</t>
+  </si>
+  <si>
+    <t>0.3804,0.3847,0.2144,0.0117</t>
+  </si>
+  <si>
+    <t>0.3227,0.8290,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.1221,0.9181,0.0172,0.0004</t>
+  </si>
+  <si>
+    <t>0.0124,0.8957,0.0433,0.0475</t>
+  </si>
+  <si>
+    <t>0.0808,0.0092,0.8482,0.0242</t>
+  </si>
+  <si>
+    <t>0.2715,0.0104,0.6475,0.0264</t>
+  </si>
+  <si>
+    <t>0.0166,0.0023,0.9526,0.0236</t>
+  </si>
+  <si>
+    <t>0.0121,0.0373,0.9716,0.0006</t>
+  </si>
+  <si>
+    <t>0.0052,0.9853,0.0174,0.0005</t>
+  </si>
+  <si>
+    <t>0.0073,0.0031,0.9908,0.0009</t>
+  </si>
+  <si>
+    <t>0.0045,0.7269,0.0047,0.8093</t>
+  </si>
+  <si>
+    <t>0.0101,0.9741,0.0113,0.0069</t>
+  </si>
+  <si>
+    <t>0.0102,0.9796,0.0155,0.0011</t>
+  </si>
+  <si>
+    <t>0.0011,0.9971,0.0044,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.0247,0.9682,0.0078</t>
+  </si>
+  <si>
+    <t>0.0033,0.0345,0.9906,0.0007</t>
+  </si>
+  <si>
+    <t>0.0104,0.0231,0.9768,0.0063</t>
+  </si>
+  <si>
+    <t>0.3013,0.0007,0.8431,0.0016</t>
+  </si>
+  <si>
+    <t>0.0089,0.0062,0.9828,0.0018</t>
+  </si>
+  <si>
+    <t>0.0070,0.0061,0.9840,0.0015</t>
+  </si>
+  <si>
+    <t>0.9900,0.0112,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9946,0.0054,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0015,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0360,0.3069,0.9252,0.0426</t>
+  </si>
+  <si>
+    <t>0.9898,0.0115,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0022,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0028,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.0021,0.9669,0.6684,0.0006</t>
+  </si>
+  <si>
+    <t>0.0434,0.0642,0.9052,0.0104</t>
+  </si>
+  <si>
+    <t>0.0026,0.7763,0.6063,0.0101</t>
+  </si>
+  <si>
+    <t>0.0007,0.9383,0.9690,0.0004</t>
+  </si>
+  <si>
+    <t>0.0023,0.0030,0.9928,0.0019</t>
+  </si>
+  <si>
+    <t>0.0234,0.9559,0.0231,0.0004</t>
+  </si>
+  <si>
+    <t>0.0101,0.9900,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9561,0.0152,0.0276,0.0031</t>
+  </si>
+  <si>
+    <t>0.9146,0.0297,0.0646,0.0022</t>
+  </si>
+  <si>
+    <t>0.0044,0.0272,0.9897,0.0042</t>
+  </si>
+  <si>
+    <t>0.0002,0.9898,0.9787,0.0001</t>
+  </si>
+  <si>
+    <t>0.0065,0.9195,0.5907,0.0011</t>
+  </si>
+  <si>
+    <t>0.0016,0.9948,0.0586,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.9844,0.5178,0.0003</t>
+  </si>
+  <si>
+    <t>0.0126,0.0007,0.0020,0.9927</t>
+  </si>
+  <si>
+    <t>0.0006,0.0271,0.0005,0.9979</t>
+  </si>
+  <si>
+    <t>0.0117,0.0012,0.0005,0.9947</t>
+  </si>
+  <si>
+    <t>0.0033,0.0014,0.0007,0.9976</t>
+  </si>
+  <si>
+    <t>0.0280,0.0016,0.0021,0.9865</t>
+  </si>
+  <si>
+    <t>0.0036,0.0085,0.0011,0.9959</t>
+  </si>
+  <si>
+    <t>0.0004,0.9917,0.8407,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.6056,0.9853,0.0003</t>
+  </si>
+  <si>
+    <t>0.0127,0.9562,0.0824,0.0044</t>
+  </si>
+  <si>
+    <t>0.0032,0.3431,0.9364,0.0014</t>
+  </si>
+  <si>
+    <t>0.0035,0.8950,0.7895,0.0006</t>
+  </si>
+  <si>
+    <t>0.0022,0.9088,0.8611,0.0007</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0015,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9971,0.0034,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0013,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0026,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0126,0.0014,0.9888,0.0046</t>
+  </si>
+  <si>
+    <t>0.0113,0.0063,0.9864,0.0009</t>
+  </si>
+  <si>
+    <t>0.8385,0.0059,0.1872,0.0070</t>
+  </si>
+  <si>
+    <t>0.0187,0.0017,0.9775,0.0048</t>
+  </si>
+  <si>
+    <t>0.0119,0.9859,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.0117,0.9907,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.1109,0.9183,0.0032,0.0032</t>
+  </si>
+  <si>
+    <t>0.0457,0.9591,0.0047,0.0005</t>
+  </si>
+  <si>
+    <t>0.0035,0.9947,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.9953,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.7637,0.4731,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.7808,0.0328,0.1757,0.0319</t>
+  </si>
+  <si>
+    <t>0.0083,0.0054,0.9866,0.0026</t>
+  </si>
+  <si>
+    <t>0.7976,0.0797,0.1278,0.0116</t>
+  </si>
+  <si>
+    <t>0.5177,0.0737,0.4804,0.0257</t>
+  </si>
+  <si>
+    <t>0.0484,0.0182,0.2520,0.8325</t>
+  </si>
+  <si>
+    <t>0.0053,0.9915,0.0122,0.0003</t>
+  </si>
+  <si>
+    <t>0.0045,0.9896,0.0019,0.0025</t>
+  </si>
+  <si>
+    <t>0.0014,0.9900,0.0181,0.0045</t>
+  </si>
+  <si>
+    <t>0.0011,0.9953,0.0627,0.0005</t>
+  </si>
+  <si>
+    <t>0.0020,0.9969,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.8512,0.2209,0.0069,0.0015</t>
+  </si>
+  <si>
+    <t>0.8995,0.1587,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.9969,0.0019,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9960,0.0007,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9918,0.0041,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0113,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9935,0.0070,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.6817,0.9862,0.0006</t>
+  </si>
+  <si>
+    <t>0.0039,0.8704,0.8509,0.0005</t>
+  </si>
+  <si>
+    <t>0.0486,0.0407,0.9235,0.0116</t>
+  </si>
+  <si>
+    <t>0.0056,0.0157,0.9868,0.0004</t>
+  </si>
+  <si>
+    <t>0.9333,0.0198,0.0264,0.0052</t>
+  </si>
+  <si>
+    <t>0.1880,0.0362,0.8299,0.0140</t>
+  </si>
+  <si>
+    <t>0.1925,0.0041,0.9244,0.0020</t>
+  </si>
+  <si>
+    <t>0.8083,0.0592,0.1211,0.0227</t>
+  </si>
+  <si>
+    <t>0.1176,0.0027,0.0022,0.9574</t>
+  </si>
+  <si>
+    <t>0.0001,0.0126,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0075,0.0046,0.0012,0.9948</t>
+  </si>
+  <si>
+    <t>0.0039,0.0011,0.0006,0.9981</t>
+  </si>
+  <si>
+    <t>0.0010,0.9887,0.3257,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0120,0.9862,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9953,0.0010,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.8394,0.2873,0.0040,0.0017</t>
+  </si>
+  <si>
+    <t>0.9838,0.0007,0.0007,0.0134</t>
+  </si>
+  <si>
+    <t>0.9365,0.0012,0.0007,0.0939</t>
+  </si>
+  <si>
+    <t>0.9893,0.0101,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.0503,0.2208,0.9016,0.0695</t>
+  </si>
+  <si>
+    <t>0.8800,0.0008,0.0010,0.2111</t>
+  </si>
+  <si>
+    <t>0.9745,0.0050,0.0006,0.0140</t>
+  </si>
+  <si>
+    <t>0.1512,0.8598,0.0104,0.0044</t>
+  </si>
+  <si>
+    <t>0.9231,0.0663,0.0080,0.0045</t>
+  </si>
+  <si>
+    <t>0.9686,0.0157,0.0073,0.0025</t>
+  </si>
+  <si>
+    <t>0.0812,0.8521,0.0646,0.0046</t>
+  </si>
+  <si>
+    <t>0.9491,0.0181,0.0235,0.0019</t>
+  </si>
+  <si>
+    <t>0.9753,0.0182,0.0044,0.0007</t>
+  </si>
+  <si>
+    <t>0.9975,0.0009,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0009,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9891,0.0065,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9959,0.0027,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9960,0.0006,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9265,0.1354,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.8865,0.1807,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.8521,0.2063,0.0013,0.0027</t>
+  </si>
+  <si>
+    <t>0.8870,0.1807,0.0027,0.0017</t>
+  </si>
+  <si>
+    <t>0.9893,0.0163,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9590,0.0543,0.0036,0.0031</t>
+  </si>
+  <si>
+    <t>0.9957,0.0042,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9730,0.0420,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.0015,0.0339,0.9973,0.0011</t>
+  </si>
+  <si>
+    <t>0.9951,0.0036,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.0034,0.0009,0.9960,0.0003</t>
+  </si>
+  <si>
+    <t>0.0026,0.0115,0.9943,0.0005</t>
+  </si>
+  <si>
+    <t>0.0277,0.0063,0.9801,0.0020</t>
+  </si>
+  <si>
+    <t>0.0045,0.1765,0.9655,0.0023</t>
+  </si>
+  <si>
+    <t>0.0034,0.0016,0.9942,0.0005</t>
+  </si>
+  <si>
+    <t>0.0122,0.0012,0.9894,0.0011</t>
+  </si>
+  <si>
+    <t>0.0037,0.0019,0.9922,0.0006</t>
+  </si>
+  <si>
+    <t>0.3402,0.0131,0.7499,0.0111</t>
+  </si>
+  <si>
+    <t>0.0181,0.0045,0.9784,0.0047</t>
+  </si>
+  <si>
+    <t>0.5644,0.0492,0.5183,0.0072</t>
+  </si>
+  <si>
+    <t>0.1189,0.2843,0.6419,0.0014</t>
+  </si>
+  <si>
+    <t>0.1103,0.5207,0.5082,0.0055</t>
+  </si>
+  <si>
+    <t>0.2660,0.2617,0.3815,0.0035</t>
+  </si>
+  <si>
+    <t>0.8348,0.0327,0.1750,0.0088</t>
+  </si>
+  <si>
+    <t>0.5920,0.0632,0.4126,0.0195</t>
+  </si>
+  <si>
+    <t>0.8492,0.3552,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.1858,0.9039,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.8918,0.1911,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9949,0.0066,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9853,0.0395,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.4221,0.5429,0.0602,0.0050</t>
+  </si>
+  <si>
+    <t>0.8914,0.0023,0.0906,0.0090</t>
+  </si>
+  <si>
+    <t>0.8700,0.0089,0.0129,0.0699</t>
+  </si>
+  <si>
+    <t>0.5787,0.0203,0.4851,0.0129</t>
+  </si>
+  <si>
+    <t>0.8401,0.0547,0.0556,0.0576</t>
+  </si>
+  <si>
+    <t>0.0028,0.0027,0.9898,0.0146</t>
+  </si>
+  <si>
+    <t>0.0320,0.0952,0.8997,0.0156</t>
+  </si>
+  <si>
+    <t>0.0613,0.0287,0.9261,0.0030</t>
+  </si>
+  <si>
+    <t>0.0894,0.0297,0.8688,0.0078</t>
+  </si>
+  <si>
+    <t>0.0100,0.0032,0.9839,0.0010</t>
+  </si>
+  <si>
+    <t>0.9977,0.0009,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9970,0.0012,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0010,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0015,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9943,0.0028,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0178,0.0499,0.9840,0.0042</t>
+  </si>
+  <si>
+    <t>0.2043,0.3027,0.4936,0.0104</t>
+  </si>
+  <si>
+    <t>0.8695,0.0858,0.0398,0.0133</t>
+  </si>
+  <si>
+    <t>0.0173,0.0046,0.9819,0.0030</t>
+  </si>
+  <si>
+    <t>0.0036,0.0037,0.9868,0.0034</t>
+  </si>
+  <si>
+    <t>0.0509,0.0248,0.9081,0.0047</t>
+  </si>
+  <si>
+    <t>0.0064,0.0064,0.9932,0.0006</t>
+  </si>
+  <si>
+    <t>0.0351,0.0066,0.9588,0.0012</t>
+  </si>
+  <si>
+    <t>0.0024,0.0127,0.9944,0.0018</t>
+  </si>
+  <si>
+    <t>0.0016,0.0014,0.9967,0.0008</t>
+  </si>
+  <si>
+    <t>0.1710,0.0584,0.8009,0.0144</t>
+  </si>
+  <si>
+    <t>0.3597,0.0057,0.7136,0.0142</t>
+  </si>
+  <si>
+    <t>0.9062,0.0095,0.0967,0.0045</t>
+  </si>
+  <si>
+    <t>0.9615,0.0016,0.0148,0.0066</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0027,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0060,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0199,0.0087,0.9684,0.0018</t>
+  </si>
+  <si>
+    <t>0.0061,0.0514,0.9794,0.0030</t>
+  </si>
+  <si>
+    <t>0.0188,0.0238,0.9703,0.0087</t>
+  </si>
+  <si>
+    <t>0.0159,0.0114,0.9649,0.0041</t>
+  </si>
+  <si>
+    <t>0.0083,0.0082,0.9813,0.0019</t>
+  </si>
+  <si>
+    <t>0.0227,0.0037,0.9378,0.0491</t>
+  </si>
+  <si>
+    <t>0.1285,0.0082,0.9162,0.0019</t>
+  </si>
+  <si>
+    <t>0.0256,0.0060,0.9070,0.0431</t>
+  </si>
+  <si>
+    <t>0.4547,0.0607,0.0029,0.4988</t>
+  </si>
+  <si>
+    <t>0.0146,0.0369,0.0011,0.9854</t>
+  </si>
+  <si>
+    <t>0.0836,0.0009,0.0018,0.9624</t>
+  </si>
+  <si>
+    <t>0.0037,0.0003,0.0009,0.9976</t>
+  </si>
+  <si>
+    <t>0.0027,0.0014,0.0003,0.9985</t>
+  </si>
+  <si>
+    <t>0.9228,0.0159,0.0059,0.0307</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1964,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1992,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2037,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2065,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2079,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2107,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2121,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2132,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2146,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2160,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,10 +2188,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,10 +2202,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2216,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,10 +2230,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,10 +2244,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2261,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2272,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2300,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2356,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2398,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2415,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2440,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2454,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2471,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2482,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2524,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2552,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2566,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2580,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2594,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2608,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2650,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2723,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2737,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2765,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2779,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2793,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2804,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2832,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2874,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2919,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2944,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2958,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2972,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2989,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3000,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3028,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3042,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3056,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3070,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3084,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3098,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3112,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3129,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3154,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3311,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3325,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3451,7 +3448,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3462,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3476,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3490,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3504,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3605,7 +3602,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3616,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3630,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3644,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3672,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3826,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3840,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3899,7 +3896,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>403</v>
@@ -3941,7 +3938,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3969,7 +3966,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3980,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3994,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4022,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4109,7 +4106,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4148,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4190,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4515,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4585,7 +4582,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4596,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4610,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4624,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4638,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4711,7 +4708,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4767,7 +4764,7 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
         <v>465</v>
@@ -5008,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>363</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5016,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5114,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5170,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5243,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5257,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5271,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5285,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5299,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5313,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5366,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5394,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5408,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5450,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5464,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5478,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5492,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5509,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
